--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>40500</v>
+        <v>40800</v>
       </c>
       <c r="C419" t="n">
-        <v>120479</v>
+        <v>623363</v>
       </c>
       <c r="D419" t="n">
-        <v>43101</v>
+        <v>42997</v>
       </c>
       <c r="E419" t="n">
-        <v>42255</v>
+        <v>42102</v>
       </c>
       <c r="F419" t="n">
-        <v>40791</v>
+        <v>40828</v>
       </c>
       <c r="G419" t="n">
-        <v>42049</v>
+        <v>41976</v>
       </c>
       <c r="H419" t="n">
-        <v>-0.1816235573461007</v>
+        <v>-0.1830443159922929</v>
       </c>
     </row>
   </sheetData>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>-0.1830443159922929</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>40100</v>
+      </c>
+      <c r="C420" t="n">
+        <v>122600</v>
+      </c>
+      <c r="D420" t="n">
+        <v>42893</v>
+      </c>
+      <c r="E420" t="n">
+        <v>42005</v>
+      </c>
+      <c r="F420" t="n">
+        <v>40675</v>
+      </c>
+      <c r="G420" t="n">
+        <v>41858</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-0.18534088476285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>40600</v>
+        <v>40500</v>
       </c>
       <c r="C421" t="n">
-        <v>15849</v>
+        <v>77144</v>
       </c>
       <c r="D421" t="n">
-        <v>42792</v>
+        <v>42778</v>
       </c>
       <c r="E421" t="n">
-        <v>42000</v>
+        <v>41978</v>
       </c>
       <c r="F421" t="n">
-        <v>40658</v>
+        <v>40647</v>
       </c>
       <c r="G421" t="n">
-        <v>41817</v>
+        <v>41801</v>
       </c>
       <c r="H421" t="n">
-        <v>-0.1861388450983826</v>
+        <v>-0.1864502442537125</v>
       </c>
     </row>
   </sheetData>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>-0.1864502442537125</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>40150</v>
+      </c>
+      <c r="C422" t="n">
+        <v>106108</v>
+      </c>
+      <c r="D422" t="n">
+        <v>42631</v>
+      </c>
+      <c r="E422" t="n">
+        <v>41933</v>
+      </c>
+      <c r="F422" t="n">
+        <v>40612</v>
+      </c>
+      <c r="G422" t="n">
+        <v>41725</v>
+      </c>
+      <c r="H422" t="n">
+        <v>-0.187929390241529</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>-0.187929390241529</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>40400</v>
+      </c>
+      <c r="C423" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D423" t="n">
+        <v>42369</v>
+      </c>
+      <c r="E423" t="n">
+        <v>41790</v>
+      </c>
+      <c r="F423" t="n">
+        <v>40589</v>
+      </c>
+      <c r="G423" t="n">
+        <v>41582</v>
+      </c>
+      <c r="H423" t="n">
+        <v>-0.190712520192289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>-0.190712520192289</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>40200</v>
+      </c>
+      <c r="C424" t="n">
+        <v>101653</v>
+      </c>
+      <c r="D424" t="n">
+        <v>42310</v>
+      </c>
+      <c r="E424" t="n">
+        <v>41745</v>
+      </c>
+      <c r="F424" t="n">
+        <v>40250</v>
+      </c>
+      <c r="G424" t="n">
+        <v>41435</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-0.1935734999318814</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>-0.1935734999318814</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>39350</v>
+      </c>
+      <c r="C425" t="n">
+        <v>292531</v>
+      </c>
+      <c r="D425" t="n">
+        <v>42131</v>
+      </c>
+      <c r="E425" t="n">
+        <v>41351</v>
+      </c>
+      <c r="F425" t="n">
+        <v>39887</v>
+      </c>
+      <c r="G425" t="n">
+        <v>41123</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-0.1996457834608124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>-0.1996457834608124</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>39200</v>
+      </c>
+      <c r="C426" t="n">
+        <v>240054</v>
+      </c>
+      <c r="D426" t="n">
+        <v>42055</v>
+      </c>
+      <c r="E426" t="n">
+        <v>40937</v>
+      </c>
+      <c r="F426" t="n">
+        <v>39634</v>
+      </c>
+      <c r="G426" t="n">
+        <v>40876</v>
+      </c>
+      <c r="H426" t="n">
+        <v>-0.204453007921216</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>39300</v>
+      </c>
+      <c r="C427" t="n">
+        <v>112976</v>
+      </c>
+      <c r="D427" t="n">
+        <v>42022</v>
+      </c>
+      <c r="E427" t="n">
+        <v>40806</v>
+      </c>
+      <c r="F427" t="n">
+        <v>39525</v>
+      </c>
+      <c r="G427" t="n">
+        <v>40784</v>
+      </c>
+      <c r="H427" t="n">
+        <v>-0.2062435530643623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>-0.2062435530643623</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>38950</v>
+      </c>
+      <c r="C428" t="n">
+        <v>121443</v>
+      </c>
+      <c r="D428" t="n">
+        <v>42077</v>
+      </c>
+      <c r="E428" t="n">
+        <v>40625</v>
+      </c>
+      <c r="F428" t="n">
+        <v>39346</v>
+      </c>
+      <c r="G428" t="n">
+        <v>40683</v>
+      </c>
+      <c r="H428" t="n">
+        <v>-0.2082092602323816</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>-0.2082092602323816</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>39400</v>
+      </c>
+      <c r="C429" t="n">
+        <v>149528</v>
+      </c>
+      <c r="D429" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E429" t="n">
+        <v>40496</v>
+      </c>
+      <c r="F429" t="n">
+        <v>39260</v>
+      </c>
+      <c r="G429" t="n">
+        <v>40585</v>
+      </c>
+      <c r="H429" t="n">
+        <v>-0.2101165800587765</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>-0.2101165800587765</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>38700</v>
+      </c>
+      <c r="C430" t="n">
+        <v>147900</v>
+      </c>
+      <c r="D430" t="n">
+        <v>41935</v>
+      </c>
+      <c r="E430" t="n">
+        <v>40291</v>
+      </c>
+      <c r="F430" t="n">
+        <v>39118</v>
+      </c>
+      <c r="G430" t="n">
+        <v>40448</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-0.2127829353262879</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>-0.2127829353262879</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>38250</v>
+      </c>
+      <c r="C431" t="n">
+        <v>93011</v>
+      </c>
+      <c r="D431" t="n">
+        <v>41707</v>
+      </c>
+      <c r="E431" t="n">
+        <v>40003</v>
+      </c>
+      <c r="F431" t="n">
+        <v>38958</v>
+      </c>
+      <c r="G431" t="n">
+        <v>40223</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-0.2171619859481131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>-0.2171619859481131</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>37400</v>
+      </c>
+      <c r="C432" t="n">
+        <v>213704</v>
+      </c>
+      <c r="D432" t="n">
+        <v>41501</v>
+      </c>
+      <c r="E432" t="n">
+        <v>39817</v>
+      </c>
+      <c r="F432" t="n">
+        <v>38446</v>
+      </c>
+      <c r="G432" t="n">
+        <v>39921</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-0.2230396450049629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>-0.2230396450049629</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>37700</v>
+      </c>
+      <c r="C433" t="n">
+        <v>87869</v>
+      </c>
+      <c r="D433" t="n">
+        <v>41303</v>
+      </c>
+      <c r="E433" t="n">
+        <v>39689</v>
+      </c>
+      <c r="F433" t="n">
+        <v>38262</v>
+      </c>
+      <c r="G433" t="n">
+        <v>39752</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-0.2263287985831338</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>-0.2263287985831338</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>36950</v>
+      </c>
+      <c r="C434" t="n">
+        <v>180026</v>
+      </c>
+      <c r="D434" t="n">
+        <v>41191</v>
+      </c>
+      <c r="E434" t="n">
+        <v>39480</v>
+      </c>
+      <c r="F434" t="n">
+        <v>37700</v>
+      </c>
+      <c r="G434" t="n">
+        <v>39457</v>
+      </c>
+      <c r="H434" t="n">
+        <v>-0.2320702205095269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>-0.2320702205095269</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>37500</v>
+      </c>
+      <c r="C435" t="n">
+        <v>178402</v>
+      </c>
+      <c r="D435" t="n">
+        <v>41098</v>
+      </c>
+      <c r="E435" t="n">
+        <v>39302</v>
+      </c>
+      <c r="F435" t="n">
+        <v>37456</v>
+      </c>
+      <c r="G435" t="n">
+        <v>39286</v>
+      </c>
+      <c r="H435" t="n">
+        <v>-0.2353982989821141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>-0.2353982989821141</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>38350</v>
+      </c>
+      <c r="C436" t="n">
+        <v>92927</v>
+      </c>
+      <c r="D436" t="n">
+        <v>40935</v>
+      </c>
+      <c r="E436" t="n">
+        <v>38835</v>
+      </c>
+      <c r="F436" t="n">
+        <v>37468</v>
+      </c>
+      <c r="G436" t="n">
+        <v>39080</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-0.2394075631069851</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>-0.2394075631069851</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>37400</v>
+      </c>
+      <c r="C437" t="n">
+        <v>135918</v>
+      </c>
+      <c r="D437" t="n">
+        <v>40826</v>
+      </c>
+      <c r="E437" t="n">
+        <v>38759</v>
+      </c>
+      <c r="F437" t="n">
+        <v>37476</v>
+      </c>
+      <c r="G437" t="n">
+        <v>39020</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-0.2405753099394717</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>-0.2405753099394717</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>85733</v>
+      </c>
+      <c r="D438" t="n">
+        <v>40731</v>
+      </c>
+      <c r="E438" t="n">
+        <v>38634</v>
+      </c>
+      <c r="F438" t="n">
+        <v>37386</v>
+      </c>
+      <c r="G438" t="n">
+        <v>38917</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-0.2425799420019074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>-0.2425799420019074</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>36600</v>
+      </c>
+      <c r="C439" t="n">
+        <v>96073</v>
+      </c>
+      <c r="D439" t="n">
+        <v>40673</v>
+      </c>
+      <c r="E439" t="n">
+        <v>38500</v>
+      </c>
+      <c r="F439" t="n">
+        <v>37391</v>
+      </c>
+      <c r="G439" t="n">
+        <v>38855</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.2437866137288103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>-0.2437866137288103</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>35900</v>
+      </c>
+      <c r="C440" t="n">
+        <v>83328</v>
+      </c>
+      <c r="D440" t="n">
+        <v>40615</v>
+      </c>
+      <c r="E440" t="n">
+        <v>38344</v>
+      </c>
+      <c r="F440" t="n">
+        <v>37101</v>
+      </c>
+      <c r="G440" t="n">
+        <v>38686</v>
+      </c>
+      <c r="H440" t="n">
+        <v>-0.2470757673069812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>-0.2470757673069812</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>34800</v>
+      </c>
+      <c r="C441" t="n">
+        <v>106866</v>
+      </c>
+      <c r="D441" t="n">
+        <v>40371</v>
+      </c>
+      <c r="E441" t="n">
+        <v>38199</v>
+      </c>
+      <c r="F441" t="n">
+        <v>36388</v>
+      </c>
+      <c r="G441" t="n">
+        <v>38319</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-0.2542184854323583</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>-0.2542184854323583</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>35500</v>
+      </c>
+      <c r="C442" t="n">
+        <v>100831</v>
+      </c>
+      <c r="D442" t="n">
+        <v>40243</v>
+      </c>
+      <c r="E442" t="n">
+        <v>38099</v>
+      </c>
+      <c r="F442" t="n">
+        <v>35908</v>
+      </c>
+      <c r="G442" t="n">
+        <v>38083</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-0.2588116229734727</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>-0.2588116229734727</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>36500</v>
+      </c>
+      <c r="C443" t="n">
+        <v>164363</v>
+      </c>
+      <c r="D443" t="n">
+        <v>40080</v>
+      </c>
+      <c r="E443" t="n">
+        <v>37924</v>
+      </c>
+      <c r="F443" t="n">
+        <v>35914</v>
+      </c>
+      <c r="G443" t="n">
+        <v>37973</v>
+      </c>
+      <c r="H443" t="n">
+        <v>-0.260952492166365</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>-0.260952492166365</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>34850</v>
+      </c>
+      <c r="C444" t="n">
+        <v>372567</v>
+      </c>
+      <c r="D444" t="n">
+        <v>39788</v>
+      </c>
+      <c r="E444" t="n">
+        <v>37473</v>
+      </c>
+      <c r="F444" t="n">
+        <v>35356</v>
+      </c>
+      <c r="G444" t="n">
+        <v>37539</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-0.2693991942546856</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/호텔신라_일별_기준주가.xlsx
+++ b/data/호텔신라_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>-0.2693991942546856</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>34600</v>
+      </c>
+      <c r="C445" t="n">
+        <v>218694</v>
+      </c>
+      <c r="D445" t="n">
+        <v>39623</v>
+      </c>
+      <c r="E445" t="n">
+        <v>37078</v>
+      </c>
+      <c r="F445" t="n">
+        <v>35137</v>
+      </c>
+      <c r="G445" t="n">
+        <v>37280</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-0.2744399680815865</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
